--- a/output/selected_news.xlsx
+++ b/output/selected_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,186 +468,241 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>보험사</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DB손해보험</t>
+          <t>우리은행</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[2026 보험, 위기와 기회] DB손해보험, '경영효율' 기반 글로벌 도약 - 메트로신문</t>
+          <t>우리은행, 생성형 AI 기반 '심층 리서치' 개발 - 초이스경제</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sat, 17 Jan 2026 23:25:09 GMT</t>
+          <t>Wed, 25 Feb 2026 00:22:38 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.metroseoul.co.kr/article/20260118500008</t>
+          <t>http://www.choicenews.co.kr/news/articleView.html?idxno=161486</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>DB손해보험은 새해 경영 키워드로 '경영효율 우위 기반의 글로벌 보험회사 도약'을 제시했다. 국내에선 손해율 등 본업 수익성의 변동성을 낮추고, 해외에선 미국 특화보험사 포테그라(Fortegra) 인수를 축으로 성장 모델과 이익 규모를 키우겠다는 구상이다.
-정종표 DB손해보험 사장./DB손해보험
-◆ 본업 흔들림 '숫자'로 확인
-DB손해보험의 올해 과제는 '성장'보다 수익구조의 안정화에 가깝다. 2025년 3분기 누적 기준 DB손해보험의 당기순이익은 1조1999억원으로 전년 동기(1조5780억원) 대비 3781억원 감소했다.
-손익의 결은 엇갈렸다. 같은 기간 보험손익은 7725억원으로 전년 동기 대비 6861억원 줄었고, 투자손익은 8897억원으로 2702억원 늘었다. 본업(보험) 둔화를 투자 성과가 일부 상쇄한 구조다. 보험손익을 보종별로 보면 장기손해보험 8004억원, 자동차보험 218억원, 일반보험 -497억원으로 집계됐다.
-정종표 DB손해보험 사장은 2026년 신년사에서 장기보험에 대해 "신계약 수익성 제고"와 "손해율 경쟁우위 확보를 위한 상품·언더라이팅(U/W) 전략"을, 자동차보험에 대해 "적정보험료 확보 및 U/W 강화"를 전면에 둔 배경도 이 같은 숫자 흐름과 맞물린다.
-건전성은 '방어'가 핵심이다. 2025년 3분기 기준 DB손해보험의 K-ICS(지급여력) 비율은 226.45%로 공시됐다. 금리·유동성 변동성이 커지는 환경에서 정종표 사장이 "유동성 및 금리하락 대응 투자손익 관리 강화"를 별도 과제로 언급한 것도 같은 맥락이다.
-DB손해보험 사옥./DB손해보험
-◆ 포테그라·AI Impact·소비자보호
-DB손해보험의 '글로벌'은 선언이 아니라 거래로 이어졌다. DB손해보험은 2025년 9월 미국 특화보험사 포테그라 발행주식 100%를 16억5000만달러(약 2조3000억원)에 인수하는 계약을 체결했다. 2026년 상반기 중 거래를 마무리할 것으로 예상된다.
-정종표 사장은 "포테그라 인수를 성공적으로 마무리하고 관리체계를 조기에 구축"하겠다고 선언했다. 미주 사업은 매출 규모에 걸맞은 수익 규모를 확보하고, 베트남은 합병 시너지를 통해 연결손익에 기여하도록 하겠다는 목표다.
-AI는 '도입'이 아니라 전사 생산성·효율화 과제(AI Impact)가 꼽힌다. 신년사에 'AI 기반 생산성·효율화 제고'가 비용구조 재설계와 함께 묶인 만큼, 2026년에는 현업 프로세스 단위의 체감 성과가 관전 포인트가 될 전망이다.
-실행 사례는 이미 나왔다. DB손해보험은 2025년 8월 AI 전문기업 티쓰리큐(T3Q)와 온톨로지 기반 '보상(청구) 자동화' 협력을 발표해 개념검증(PoC) 추진을 언급했다. 장기보험 보상청구 자동화는 DB손해보험이 업계 최초로 시도하는 도전적인 사업이다.
-마지막 축은 감독당국의 소비자 중심 제도 개혁 기조에 맞춘 소비자보호 강화다.
-정종표 사장은 신년사에서 "사전예방적 금융소비자보호로의 패러다임 전환"과 "상품 전 생애주기별 소비자보호 강화"를 내세우며 내부통제와 거버넌스 관리를 강조했다.
-결국 2026년 DB손해보험의 승부처는 손해율 변동성 축소와 자본·유동성 방어, 포테그라를 축으로 한 해외 이익 규모 확대, AI 기반 효율화가 한 흐름으로 연결되느냐다.
-정종표 사장은 "국내는 손해율 등 수익성 경쟁우위 회복을 통한 안정적 사업구조를 구축하고, 해외는 신규 성장모델과 수익규모 확대를 통해 차별화된 글로벌 경쟁력을 확보하겠다"며 "전사 역량을 집중하겠다"고 말했다.</t>
+          <t>사진=우리은행
+[초이스경제 최유림 기자] 우리은행(은행장 정진완)은 "지난 23일 은행 내부 데이터를 활용해 보고서를 자동 생성하는 생성형 인공지능(AI) 기반 '심층 리서치(Deep Research)' 개발, AX 가속화에 나섰다"고 25일 밝혔다.
+우리은행에 따르면 이번에 도입한 '심층 리서치'는 직원의 산업·기업 분석 요청에 따라 내부 금융 데이터를 수집·연계·분석해 단시간 내 전문가 수준의 보고서 초안을 제시하는 지능형 보고서 작성 지원 시스템이다. 단순 정보 나열에 그치던 기존 AI와 달리 내부 핵심 데이터를 유기적으로 연결해 맥락을 이해하는 분석 결과를 도출하며, 자료 수집·정리 시간을 획기적으로 단축해 직원들이 보다 창의적이고 전략적인 의사결정에 집중할 수 있도록 지원하는 것이 특징이다.
+이와 함께, 우리은행은 글로벌 범용 AI인 MS 코파일럿과 자체 개발 '심층 리서치'를 전략적으로 결합해 AI 업무 환경을 한 단계 고도화했다. 코파일럿이 산업 동향·뉴스 등 외부 정보를 분석하는 데 강점이 있다면, '심층 리서치'는 은행 내부의 방대한 금융 데이터를 기반으로 최적화된 보고서를 생성한다. 이에 따라 외부 인사이트와 내부 데이터를 결합함으로써 분석의 정교함과 데이터 보안성을 동시에 확보했다.
+한편, 향후에는 '심층 리서치'를 고도화해 AI-Agent 기반 서비스로 확대 적용할 계획이다. △여신 심사 △자산관리 △내부통제 등 은행 핵심 업무 전반으로 AI 활용 범위를 넓혀 의사결정을 지원하는 '지능형 인공지능 비서' 체계로 발전시켜 나갈 방침이라고 우리은행은 덧붙였다.
+옥일진 우리은행 AX혁신그룹 부행장은 "이번 개발은 당행에 최적화된 독자적인 AI 역량을 확보했다는 데 의미가 있다"며 "앞으로도 직원들이 고부가가치 업무에 집중할 수 있도록 실무 밀착형 AI 서비스를 지속 확대해 나가겠다"고 말했다.</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>보험사</t>
+          <t>은행</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KB손해보험</t>
+          <t>하나은행</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KB손해보험, AI 및 디지털 전환 가속화로 고객경험 혁신 나선다 - 리버티코리아포스트</t>
+          <t>하나은행, AI 안부서비스 도입…"시니어의 건강한 일상 지원" - 파이낸셜신문</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thu, 22 Jan 2026 08:30:18 GMT</t>
+          <t>Mon, 23 Feb 2026 01:17:54 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>http://www.lkp.news/news/articleView.html?idxno=75365</t>
+          <t>https://www.efnews.co.kr/news/articleView.html?idxno=127687</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>그래픽=리버티코리아포스트
-[리버티코리아포스트=문효근 기자]
-보험 업계의 AI 전략이 한층 진화하고 있다. 단순한 자동화나 업무적인 효율 개선을 넘어 경영 전략과 조직 시스템 등 사업 구조 전반으로 AI가 확산되는 중이다. 최근에는 AI를 상품 개발, 손해율 관리, 조직 운영 등에 접목하는 흐름이 뚜렷해지고 있다.
-◆ AI 기술 기반으로 고객경험 혁신에 적극 나서
-올해 보험사 조직개편의 핵심 중 한 부분은 AI 전환을 전사 단위에 적용시켰다는 점이다. 기존에는 디지털 전환 조직이 AI 프로젝트를 추진하는 형태가 많았다면 올해부터는 전사적인 컨트롤타워를 구축해 AI 전환을 위한 과제 개발부터 실행 등에 이르기까지 총괄하는 구조로 변모했다.
-주요 보험사들은 금융소비자 보호를 우선으로 한 AI 전환과 미래 성장동력 확보를 중점적인 목표로 제시했다. 높아지는 규제 강화와 변동성이 큰 영업 환경에서 단순한 비용 절감 차원이 아니라 시스템적인 경쟁력를 강화하려는 기조로 보인다.
-KB손해보험도 AI 및 디지털 전환에 적극적으로 나서며 미래 성장동력을 구축하는데 분주한 모습이다.
-지난 연말 조직개편을 통해 기존 DT추진본부를 AI데이터본부로 재편해 실질적인 AI 전환 실행력을 확보하고자 했다. 영업조직에는 AI 및 디지털 기반의 미래 채널 운영 모델 구축을 위한 스마트비서유닛을 신설했다.
-고객 서비스 품질 제고를 위해서는 콜센터 조직을 AI데이터본부 산하로 이동시켰고, 소비자보호본부에는 고객경험 전담 조직을 신설해 고객 접점 전반을 점검하는 시스템을 구축했다.
-&lt;본지&gt;에 KB손해보험 관계자는 “AI데이터본부 산하에 콜센터 조직을 편제했고, 소비자보호본부 산하에는 고객경험파트를 신설해 고객중심 경영을 위한 전사 컨트롤타워 운영체계를 구축했다”며 “AI 및 디지털 가속화를 통해 고객 서비스 품질을 더욱 향상시키는 한편 AI 기술을 기반으로 고객경험 혁신에 적극적으로 나설 예정”이라고 전했다.
-한편 KB손해보험은 다양한 기업과의 협업을 통해서도 디지털 사업을 확장시켜 왔다.
-지난해 LG유플러스, 인슈어테크 기업 스몰티켓과 함께 실시간 차량 데이터 기반의 상품 개발에 나섰다. KB손해보험은 양사와 업무협약을 맺고 급변하는 모빌리티 환경에 대응하는 한편 차량 데이터와 AI 기술을 접목한 차세대 자동차보험 상품 및 위험관리 서비스를 개발하기로 했다. 보험·통신·플랫폼을 유기적으로 결합한 신규 모델이라는 점과 고객의 안전운전을 유도하고 보험료 할인 혜택까지 제공하는 의미 있는 사례라는 점에서 이목을 모았다.
-◆ 다양한 AI 서비스로 디지털 전환 꾸준히 준비
-AI 전환은 구본욱 KB손해보험 대표의 디지털 혁신경영 전략의 일환이다. 구 대표 취임 이후 KB손해보험은 AI 및 디지털 전환을 꾸준히 추진해 왔다.
-2024년 4월 K-BEST 차세대 시스템을 도입해 고객 맞춤형 서비스의 경쟁력을 제고시켰다. K-BEST 차세대 시스템은 미래 환경 변화에 선제적으로 대응해 고객별 맞춤형 보험설계는 물론 심사, 관리, 지급 서비스 등이 가능한 시스템이다.
-작년 5월에는 KB금융그룹 및 계열사들과 협업해 생성형 AI 기술 활용 플랫폼인 KB GenAI 포털을 구축했다. 영업 현장과 고객의 다양한 요구에 대응할 수 있는 AI 에이전트를 개발할 수 있도록 돕는 포털이다. IT 개발 경험이 없는 직원도 자신만의 AI 에이전트를 만들어 실무에 적용할 수 있어, 생성형 AI 기술에 기반한 금융 서비스 확산이 한층 업그레이드될 것으로 기대된다.
-6월에는 보험설계사와 고객 사이 소통의 품질을 높이는 한편 고객 만족도를 향상시키기 위해 AI 기반의 화법 코칭 솔루션인 크디랩의 쏘카인드를 영업교육 현장에 도입했다.
-9월에는 접수된 자동차 사고 내용을 AI가 스스로 분석해 예상 과실 비율 등을 자동으로 산정해 주는 자동차 사고 과실 비율 안내 AI 에이전트 서비스를 선보였다.
-◆ AI 시대 걸맞은 일하는 방식 변화 추진
-10월에는 이미 상담 이력이 있는 고객에게 보다 연속적이고 일관된 상담 서비스를 제공하기 위해 상담원의 과거 상담 내용을 AI가 자동으로 요약해 안내하는 콜센터 상담지원 AI 에이전트도 도입해 업무에 활용하고 있다.
-11월에는 생성형 AI 기술을 활용한 AI 민원 해결 도우미 서비스를 도입하는 등 KB손해보험의 디지털 혁신은 고객 민원 해결에까지 도달하는 수준에 왔다.
-&lt;본지&gt;에 KB손해보험 관계자는 “AI 시대에 부합하는 임직원들의 일하는 방식의 변화를 적극적으로 추진하고 있다. 이를 통해 빠르게 변화하는 디지털 환경 속에서 뚜렷한 성과를 창출하고자 노력 중”이라고 전했다.</t>
+          <t>AI 목소리 든든이 통해 정기적으로 일상 안부 묻고 생활 정보도 제공
+하나은행이 시니어 고객의 건강한 일상을 지원하기 위해 인공지능(AI) 기반 맞춤형 전화 서비스인 'AI 안부서비스'를 도입하고 시범 운영에 나선다고 23일 밝혔다.
+AI 안부서비스는 AI 목소리 '든든이'가 고객이 정한 요일과 시간에 정기적으로 전화를 걸어 안부를 묻고 생활 정보를 제공하는 음성 통화 서비스다. 특히, 별도의 기기나 애플리케이션을 설치하지 않아도 돼 디지털 환경에 익숙하지 않은 시니어 고객도 편리하게 이용할 수 있다.
+(하나은행 제공)
+AI 목소리 든든이는 시니어들의 관심사와 생활 패턴을 반영해 맞춤형 대화 주제를 구성한다. 이를 통해 고객에게 간단한 건강 관리, 제철 음식, 문화·여가 등 일상에 도움이 되는 정보를 전달할 뿐만 아니라, 혼자 생활하거나 가족과 떨어져 지내는 고객에게 정서적 안정도 제공한다.
+서비스 신청 방법은 온·오프라인을 통해 하나더넥스트 상담을 받은 고객 중 선착순 300여 명에게 AI 안부서비스를 무료로 사용할 수 있는 쿠폰이 제공되고, 쿠폰에 안내된 웹 페이지를 통해 고객이 직접 서비스를 신청할 수 있다. 하나은행은 시범 운영 기간 중 고객 의견을 반영해 서비스 대상과 기능을 단계적으로 확대해 나갈 계획이다.
+이은정 하나은행 WM본부장은 "시니어 고객의 건강한 일상을 지원하고 디지털 포용성을 제고하기 위해 전화 기반의 AI 서비스를 새롭게 출시했다"며 "앞으로도 하나더넥스트를 중심으로 시니어 고객의 금융은 물론 일상까지 함께 지원하는 다양한 서비스를 지속적으로 선보이겠다"고 말했다.
+한편, 하나금융그룹의 시니어 특화 브랜드인 하나더넥스트는 은퇴 설계, 자산관리, 상속·증여 등 생애 전반에 걸친 금융 솔루션과 라이프케어 서비스를 제공하고 있다. 상담을 원하는 고객은 ARS, 하나더넥스트 공식 홈페이지, 하나원큐 앱 등을 통해 신청할 수 있다. [파이낸셜신문=임영빈 기자]
+저작권자 © 파이낸셜신문 무단전재 및 재배포 금지</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>보험사</t>
+          <t>카드사</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>교보생명</t>
+          <t>NH농협카드</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>교보생명, 청각장애 고객 대상 실시간 원격 수어통역 - 매일경제</t>
+          <t>농협은행, 'AI, 금융 일상에' 전면 전략 전환... 에이전틱 AI 뱅크 선언 - 프레스맨</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mon, 26 Jan 2026 07:01:36 GMT</t>
+          <t>Fri, 13 Feb 2026 12:59:51 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.mk.co.kr/news/special-edition/11943376</t>
+          <t>https://www.pressman.kr/news/articleView.html?idxno=99995</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>사진 확대 교보생명의 고객 상담 편의성을 높이기 위한 디지털고객창구. 교보생명
-교보생명은 금융소비자 보호와 포용적 금융 실천을 위해 금융 취약계층 맞춤형 서비스를 대폭 강화하고 있다. 상품 개발 단계부터 디지털 격차 해소까지 전 과정에 걸쳐 실질적인 혜택을 제공함으로써 누구나 소외되지 않는 금융 환경을 조성하겠다는 취지다.올해 교보생명은 주요 경영 과제로 고객 완전 보장과 금융소비자 보호를 내걸고 사회적 책임 강화에 집중하고 있다. 신창재 교보생명 대표이사 겸 이사회 의장은 연초 보험의 완전 가입과 유지, 정당한 보험금 지급을 통한 소비자 보호가 생명보험 정신의 실천임을 강조하며 현장의 변화를 독려했다.특히 청각장애 고객을 위한 서비스 혁신이 눈에 띈다. 교보생명은 한국지능정보사회진흥원의 '손말이음센터'와 협력해 실시간 통신 중계 서비스를 제공하고 있다. 수어 통역사가 고객의 영상이나 문자를 음성으로 변환해 상담사에게 전달하는 방식이다. 2024년부터는 전국 5개 디지털 고객창구에 '아바타 수어 서비스'를 도입해 화상 상담을 지원하고 있으며 이를 점진적으로 확대할 계획이다.고령층과 장애인을 위한 제도적 보완도 이뤄졌다. 고령 고객의 이해를 돕기 위해 보험 계약 안내물을 큰 글씨로 제작하고, 핵심 요약 자료인 우선안내 확인서를 통해 주요 사항을 명확히 전달하고 있다. 아울러 치매나 중증질환으로 직접 청구가 어려운 상황을 대비해 지정대리청구인 제도를 운영하고, 대출 이용 시 본인과 지정인 모두에게 정보를 알리는 지정인 알림 서비스도 시행 중이다.금융 소외 지역과 계층을 아우르는 전용 상품 공급에도 적극적이다. 장애인 전용 암·건강보험인 '교보곰두리보장보험'을 비롯해 자립준비청년의 자산 형성을 돕는 '교보청년저축보험'을 운영하고 있다.[차창희 기자]</t>
+          <t>디자인=김승종기자/이미지=농협은행, 게티이미지뱅크
+NH농협은행이 AI를 은행 운영의 핵심 축으로 삼는 'Agentic AI Bank(에이전틱 AI 뱅크)' 전환을 전면 선언했다. 6,200억원 규모의 코어뱅킹 재구축 프로젝트와 AI 무인점포, 원화 스테이블코인 생태계 구축까지 올해 들어 AI 중심의 디지털 혁신을 동시다발적으로 추진하고 있다. '2026년은 AI 에이전트의 해'라는 글로벌 금융권 트렌드를 국내 시중은행 중 가장 적극적으로 선점하겠다는 포석이다.
+'AI Agent First'... 글로벌 트렌드 선점
+NH농협은행 AI데이터부문은 지난달 서울 본사에서 '사업추진 결의대회'를 열고 'Agentic AI Bank'로의 본격 도약을 선언했다. 'AI가 고객들의 금융 일상에 자연스레 스며드는 은행'을 만들겠다는 비전이다.
+이날 결의대회에서는 'AI Agent First' 전략을 중심으로 금융서비스 혁신 방향을 논의했다. AI기본법, STO(토큰증권) 법제화 등 규제 동향과 AI 트렌드 강연도 진행해 임직원들의 사업 추진 역량을 강화했다.
+'에이전틱 AI(Agentic AI)'는 사람의 지시 없이도 스스로 판단하고 업무를 수행하는 자율형 AI를 의미한다.
+액센추어의 '2026 은행업 트렌드' 보고서에 따르면, 향후 3년 내 57%의 은행 임원이 AI 에이전트가 리스크·컴플라이언스·감사, 사기 탐지, 거래 모니터링 기능에 완전히 내재화될 것으로 전망했다. 56%는 신용평가·대출 심사, 고객확인(KYC) 영역까지 AI 에이전트가 광범위하게 도입될 것으로 예상했다.
+김주식 농협은행 AI데이터부문 부행장은 "고객을 미소짓게 하고 고객과의 동반성장을 실현하는 농협은행을 만들기 위해 전사적 AX(AI 전환)를 지속적으로 추진하겠다"고 밝혔다.
+6,200억 투입 '프로젝트 NEO'... 코어뱅킹 전면 재구축
+농협은행의 AI 전환 전략의 근간은 코어뱅킹 시스템 전면 개편이다. 농협은행은 지난달 경기도 의왕 NH통합IT센터에서 '프로젝트 NEO' 본사업에 착수한다고 밝혔다.
+프로젝트 NEO는 'Next, Evolutionary, Omni-Banking'의 약자로, 총 6,200억원을 투자해 2028년 1월까지 계정계 시스템을 전면 재구축하는 사업이다. 2024년부터 추진해온 차세대 프로젝트의 최종 단계로, 금융권 차세대 사업 중 단일 계약 규모로는 최대 수준이다. LG CNS가 사업을 맡아 27개월간 진행한다.
+주요 개선 사항은 ▲IT 기술 구조 전면 개편 ▲비대면·대면 통합 프로세스 구현 ▲금융상품 관리시스템 개선 ▲사용자 중심 엔드 투 엔드(End to End) 프로세스 자동화 ▲고객 서식·서류의 디지털 관리체계 구축 등이다.
+LG CNS는 금융거래 시스템을 업무 단위별로 분리해 독립 운영이 가능한 구조로 전환하고 비대면 전용 코어뱅킹 시스템을 별도 구축한다. AI 보안 솔루션 '시큐엑스퍼(SecuXper) AI'와 시스템 검증 솔루션 '퍼펙트윈(PerfecTwin)' 등 자체 기술도 적용된다.
+정동훤 농협은행 테크솔루션부문 부행장은 "이번 사업은 농협은행 계정계 혁신의 중심점이 될 것"이라며 "성공적인 사업 완수를 통해 초개인화 금융으로 고객을 미소짓게 하겠다"고 밝혔다.
+AI가 먼저 인사하는 은행... 'NH디지털스테이션' 개점
+코어뱅킹 개편과 함께 고객 접점에서의 AI 혁신도 본격화됐다. 농협은행은 지난달 말 AI 기술을 접목한 미래형 무인점포 'NH디지털스테이션' 위례점을 개점했다.
+NH디지털스테이션은 AI 기반 차세대 금융기기 'NH AI STM(Smart Teller Machine)'을 중심으로 화상상담 디지털데스크와 ATM을 갖춘 무인점포다.
+가장 눈에 띄는 점은 쌍방향 금융 서비스 구현이다. 고객이 기기 앞에 서면 AI가 얼굴을 인식해 먼저 인사와 안내를 시작한다. 단순히 화면을 보고 조작하던 기존 방식을 넘어, LLM(대규모언어모델) 기반으로 고객과 기기가 실시간 대화하며 금융 거래를 지시하거나 궁금한 점에 대한 답을 얻을 수 있다.
+NH AI STM은 입출금, 이체, 체크카드 발급 등 총 17종의 업무를 지원한다. 얼굴과 장정맥을 활용한 다중 생체인증을 적용해 카드나 통장 없이도 안전한 거래가 가능하다. 전산 조작에 익숙하지 않은 고령층과 장애인 등 금융취약계층의 이용 문턱을 낮추는 데도 기여할 전망이다.
+농협은행은 위례점을 시작으로 주요 거점에 디지털 무인점포와 NH AI STM 서비스를 순차적으로 확대해 나갈 계획이다.
+원화 스테이블코인 생태계 구축... 글로벌 블록체인과 연결
+농협은행의 AI 전환 전략은 디지털자산 영역까지 확장되고 있다. 농협은행은 지난 2일 글로벌 디지털자산 인프라 기업 파이어블록스(Fireblocks)와 '택스리펀드 디지털화 PoC와 원화 스테이블코인 생태계 구성방안'을 주제로 전략 미팅을 진행했다.
+이번 미팅에는 농협은행 AI데이터부문 임원과 파이어블록스 본사 스테픈 리차드슨(Stephen Richardson) 전략담당임원(CSO)을 비롯한 글로벌·아시아 세일즈 책임자들이 참석했다.
+양사가 진행 중인 '택스리펀드 디지털화 PoC'는 지난해 11월 착수해 올해 1월 설계를 마무리했으며, 4월까지 개발과 테스트를 완료할 예정이다.
+해외 관광객이 종이 서류로 부가세를 환급받던 절차를 블록체인 기반으로 디지털화하는 프로젝트다. 파이어블록스, 아발란체(Avalanche), 마스터카드, 월드페이 등 글로벌 기술·결제 기업과 공동으로 추진하고 있다.
+양사는 원화 스테이블코인이 금융 인프라와 디지털자산 서비스 전반을 연결하는 핵심 결제레일(Payment Rail)로 발전할 수 있다는 점에 공감했다. 은행 중심의 신뢰 기반 구조를 글로벌 블록체인 네트워크와 결합하는 협력 모델을 구체화하고 있다.
+이와 별도로 농협은행은 자체 EVM(이더리움 가상머신) 기반 블록체인 메인넷을 활용해 스테이블코인과 STO에 토큰 프로토콜을 적용하는 PoC도 추진 중이다. K팝 저작권 등을 기초자산으로 한 토큰증권 청약·배정·청산 전 과정을 설계·테스트하고 있다.
+농협은행 관계자는 "원화 스테이블코인을 중심으로 한 디지털자산 생태계 구축을 통해 제도화 방향성에 맞춰 글로벌 금융 인프라와의 연결과 국내 금융 혁신을 동시에 추진하겠다"고 밝혔다.
+농협은행의 이 같은 행보는 글로벌 금융권의 흐름과 맞닿아 있다. 2026년은 AI 에이전트가 파일럿 단계를 넘어 본격적인 프로덕션 스케일로 확대되는 해가 될 것으로 전망된다.
+농협은행은 코어뱅킹 재구축(프로젝트 NEO), AI 무인점포(NH디지털스테이션), 디지털자산 생태계(원화 스테이블코인)라는 세 축을 중심으로 'Agentic AI Bank' 전환을 가속화할 계획이다. AI가 단순 보조 도구가 아니라 금융 서비스의 핵심 운영 체계로 자리잡는 '초연결 디지털 네이티브 뱅크'를 목표로 하고 있다. [프레스맨]
+저작권자 © 프레스맨 무단전재 및 재배포 금지</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[금융 AI 대전환②] 신한, 1부서 1에이전트로 AX 전면화…거버넌스도 정비 - v.daum.net</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Sat, 14 Feb 2026 15:02:20 GMT</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://v.daum.net/v/20260215000220771?f=p</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>조직 학습 구조 전환 시동…현업이 직접 설계·적용
+신한금융그룹이 '1부서 1에이전트' 전략을 통해 현업 주도형 인공지능 전환(AX) 전략을 본격화하고 있다. /신한금융그룹
+금융산업은 데이터와 리스크를 축으로 움직이는 대표적 데이터 산업이다. 고금리·저성장 기조가 구조화되면서 금융회사들은 비용 효율화, 정교한 리스크 관리, 초개인화된 고객 서비스라는 복합 과제를 동시에 떠안고 있다. 인공지능(AI)은 이 난제를 풀 핵심 수단으로 부상했다. 금융당국이 생성형 AI와 클라우드, 업무 자동화 기술의 활용 범위를 단계적으로 넓히면서 금융권의 AI 전환은 파일럿을 넘어 현업 전반으로 확산되는 국면이다. &lt;더팩트&gt;는 5대 금융지주의 AI 전략과 투자 방향을 비교·분석하고 금융 AI 전환이 실질적인 경쟁력 강화로 이어지고 있는지를 들여다본다. 아울러 내부통제와 인력 재배치 등 구조적 과제가 무엇인지도 함께 짚어본다. &lt;편집자주&gt;
+[더팩트 | 김태환 기자] 신한금융그룹이 인공지능(AI)을 일부 부서의 실험 단계에서 전사 업무 체계로 확산하는 '현업 주도형 AX(인공지능 전환)' 전략을 본격화하고 있다. 그룹 차원의 AI 윤리 원칙과 위험관리 체계를 정비하는 동시에, 모든 부서가 AI를 직접 업무에 접목하도록 유도하는 '1부서 1 에이전트(Agent)' 캠페인을 추진하며 실행력 강화에 나선 모습이다.
+신한금융은 인공지능 전환(AX)과 디지털 전환(DX)을 선택적 혁신 과제가 아닌 그룹 경쟁력과 직결된 전략 과제로 인식하고 있다. 고금리·저성장 환경에서 비용 효율화와 리스크 관리, 고객 맞춤형 서비스 고도화라는 복합 과제를 동시에 풀어야 하는 상황에서 AI를 핵심 실행 수단으로 삼겠다는 구상이다. 단순 기술 도입이 아니라 '일하는 방식'과 '사업 방식'의 전환을 촉발하는 변수로 규정했다는 점이 특징이다.
+AX 가속화와 함께 신한금융은 그룹 차원의 AI 거버넌스를 구축했다. AI 윤리 원칙을 제정하고, 각 계열사 업무 특성에 맞는 위험관리 체계를 구체화했다.
+특히 준법·정보보호·소비자보호·리스크 담당 임원이 참여하는 그룹 협의체를 구성해 AI 활용 전반에 대한 정책을 공유·조율하고 있다. AI 모델 도입과 서비스 확산이 내부통제 체계 밖으로 벗어나지 않도록 사전 점검과 승인·모니터링 절차를 병행한다는 설명이다.
+AI 활용 측면에서는 외부 상용 모델과 내부 자체 모델을 병행하는 하이브리드 방식을 택했다. 서비스 특성과 민감도에 따라 모델을 선택적으로 적용해 효율성과 보안을 동시에 확보하겠다는 구상이다.
+동시에 전 직원이 활용 가능한 AI 기반 인프라를 구축해 현업 접근성을 높이고 있다. 특정 부서나 디지털 조직에 국한된 프로젝트가 아니라, 전사적 업무 도구로 정착시키겠다는 방향성이다.
+신한금융은 SaaS 망분리 규제 완화, 금융권 AI 위험관리 프레임워크 등 제도 환경 변화를 지속 모니터링하고 있다. /신한금융그룹
+올해 신한금융은 전 그룹사를 대상으로 '1부서 1 에이전트(Agent)' 캠페인을 추진한다. AI 에이전트는 반복 업무나 문서 작성 등에만 자동화가 이루어진 것이 아니라 업무 프로세스 전 과정을 스스로 판단하고 분석하는 자동화 단계의 AI를 의미한다.
+예를 들어, 생성형 AI의 경우 "연체율 추이를 알려줘"라고 지시하면, 관련 보고서를 요약하는 수준에 그친다. AI 에이전트는 같은 질문에 대해 데이터 조회, 분석, 보고서 작성, 메일 발송, 업무 내용 저장 등 더욱 능동적으로 업무를 보조하게 된다.
+이러한 AI에이전트를 1부서별 1개씩 배치한다면 모든 부서가 본인 업무에 AI를 접목하고, 각 조직 특성에 맞는 AI 활용 사례를 발굴·적용하도록 유도할 수 있다는 설명이다.
+더 나아가 본격적으로 다가올 AI 에이전트 시대에 대비해 현업이 직접 문제를 정의하고 솔루션을 설계하는 구조를 만들어갈 수 있다고 신한금융은 설명한다. 중앙 조직이 일괄 개발해 배포하는 방식이 아니라, 현업 주도 실행 모델을 통해 조직 학습 효과를 축적하겠다는 전략으로 풀이된다.
+아울러 신한금융은 SaaS 망분리 규제 완화, 금융권 AI 위험관리 프레임워크 등 제도 환경 변화를 지속 모니터링하고 있다. AI 활용이 확대될수록 규제·승인 절차의 민첩성 역시 중요해질 수밖에 없다는 판단이다.
+신한금융 관계자는 "금융회사의 책임성 확보를 전제로 정책적 지원이 병행될 경우, AI 도입 속도와 서비스 혁신 범위가 한층 확대될 수 있다"고 설명했다.
+금융업계 관계자는 "신한금융의 전사적 AX 전략이 실제 성과로 이어지기 위해서는 데이터 품질 고도화, 현업 역량 축적, 위험관리 정교화가 병행돼야 한다는 과제도 남는다"면서 "확산의 속도와 통제의 균형을 어떻게 맞추느냐가 신한 AX 전략의 성패를 가를 변수로 떠오르고 있다"고 말했다.
+kimthin@tf.co.kr
+발로 뛰는 더팩트는 24시간 여러분의 제보를 기다립니다.
+▶카카오톡: '더팩트제보' 검색
+▶이메일: jebo@tf.co.kr
+▶뉴스 홈페이지: http://talk.tf.co.kr/bbs/report/write</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>보험사</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>신한라이프</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>신한라이프, '쏠라체' 1호 개소·KB라이프 복합점포 가동…금융지주 시너지 잰걸음 [보험사 시니어 금융 전략] - 한국금융신문</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Wed, 21 Jan 2026 08:55:19 GMT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://www.fntimes.com/html/view.php?ud=2026012113291239369efc5ce4ae_18</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>금융·주거·의료 결합한 그룹 시니어 전략
-신한라이프케어 첫 번째 프리미엄 요양원 ‘쏠라체(SOLÀCE) 홈 미사’. 사진제공=신한라이프 신한라이프, '쏠라체' 1호 개소·KB라이프 복합점포 가동…금융지주 시너지 잰걸음 [보험사 시니어 금융 전략] 이미지 확대보기
-진옥동 닫기 진옥동 기사 모아보기
-정상혁 닫기 정상혁 기사 모아보기
-그룹 통합 시니어 모델 구축… 원스톱 노후 지원
-서울 역삼동 KB라이프타워에 마련된 에이지테크랩(Age Tech Lab)에서 관계자들이 전동휠체어 체험을 하고 있다. 사진제공=KB금융 신한라이프, '쏠라체' 1호 개소·KB라이프 복합점포 가동…금융지주 시너지 잰걸음 [보험사 시니어 금융 전략] 이미지 확대보기
-강은영 한국금융신문 기자 eykang@fntimes.com
-[한국금융신문 강은영 기자] 국내 금융지주계열 보험사들이 금융그룹과의 시너지를 앞세워 시니어 사업 확대에 속도를 내고 있다. 자산관리 중심의 전통 금융 서비스에서 나아가 생명보험사를 축으로 요양과 돌봄까지 포괄하는 전략이 본격화되면서, 금융그룹 차원의 시니어 비즈니스가 새로운 성장 축으로 부상하고 있다.21일 보험업계에 따르면, 국내 금융지주계열 보험사들은 금융그룹과 함께 요양사업을 강화하고 있다.금융그룹들은 생명보험사를 중심 축으로 은행·증권·요양 자회사 등 계열사 역량을 결합해 자산관리부터 의료·돌봄까지 아우르는 종합 시니어 서비스 구축에 속도를 내고 있다.신한라이프 시니어 전담 자회사 신한라이프케어는 지난 15일 경기도 하남시 미사지구에서 첫 번째 프리미엄 요양원 ‘쏠라체(SOLÀCE) 홈 미사’를 개소했다.‘쏠라체 홈 미사’는 시니어의 지속 가능한 삶을 위해 일상생활 수행이 어려운 어르신을 대상으로 숙식 제공과 함께 신체활동 및 인지기능 유지·향상을 고려한 종합적인 돌봄 서비스를 상시 제공하는 노인요양시설이다.특히 그룹의 시니어사업을 대표하는 상징적인 시설로 집처럼 아늑하면서도 한층 더 품격 있는 편안함을 제공할 수 있도록 설계됐다. 오감(五感) 만족을 고려한 공간 구성을 통해 어르신들이 신체·심리적 안정을 갖고 생활할 수 있도록 개발됐다.업계 최고 수준의 돌봄 인력을 배치함과 동시에 안전과 신체 편의, 스마트 돌봄을 아우르는 환경 요소들을 시설 전반에 반영했다. 1인 1실 중심의 구조를 통해 생활의 안정감을 높이고 프라이버시를 존중하고, 시력 약자를 고려해 판독성이 높은 전용 글꼴을 개발해 적용하는 등 이용 편의성도 세심하게 담아냈다.쏠라체 홈 미사 개소식에는 신한금융그룹회장과신한은행장, 정용욱 신한투자증권 신한프리미어총괄사장, 천상영 신한라이프 사장 등 그룹 경영진과 이현재 하남시장, 김철주 생명보험협회장, 정재승 KAIST 교수 등 주요 내·외빈이 참석했다.진옥동 회장은 축사를 통해 “쏠라체 홈 미사는 신한금융그룹이 선보이는 첫 시니어 시설로, 금융·주거·의료 서비스를 한 공간에 담아낸 곳”이라며 “단순히 머무는 시설이 아니라 편안한 일상이 이어지는 생활 공간이 되길 기대한다”고 말했다.신한라이프케어는 신한금융그룹의 디지털 브랜드 ‘SOL’과 이탈리아어 ‘VERACE(진정한, 진실된, 참된)’를 결합하여 개발된 ‘쏠라체(SOLÀCE)’ 브랜드를 본격적으로 운영하며 진정성과 신뢰를 바탕으로 한 시니어 돌봄 서비스를 단계적으로 확대해 나갈 계획이다.KB금융그룹은 지난 20일 서울 역삼동 KB라이프타워에 보험·요양·은행 서비스를 결합한 보험-은행 복합점포 'KB라이프 역삼센터'를 개소했다.KB금융은 시니어 고객들이 한 곳에서 연결되는 통합 서비스를 통해 더 빠르고 정확한 지원을 받을 수 있도록 지난해부터 새로운 그룹 통합 시니어 서비스 운영모델 구축을 추진해 왔다.이번에 새롭게 선보이는 'KB골든라이프 플래그십 센터'는 고객의 노후 설계를 위해 필요한 의사 결정을 돕고, 생활의 편의를 높이는 새로운 기술과 전문성을 축적해 시니어 고객의 노후 준비 과정 전반을 지원한다.KB골든라이프 플래그십 센터는 'KB라이프 역삼센터'를 중심으로, 시니어를 위한 최신 기술 체험·연구 공간인 '에이지테크 랩(Age Tech Lab)'과 요양·돌봄·주거·건강·재무 등 시니어 라이프 전반을 연구하는 'KB골든라이프 교육센터'로 구성된다.KB라이프 역삼센터에서는 보험을 넘어 자산관리와 요양·돌봄까지 아우르는 원스톱 종합 라이프 컨설팅 서비스를 제공한다. 금융업권 최초로 전문 간호사로 구성된 케어컨설턴트가 상주하며, 가족 돌봄이 필요한 고객을 위해 재가돌봄에서 요양원 입소에 이르는 종합 요양·돌봄 컨설팅을 지원한다.방문 고객은 보험PB를 통한 맞춤형 보험 진단·상담과 보험계약관리 서비스는 물론, WM 웰스매니저의 노후 소득 설계 서비스도 받을 수 있다. 퇴직연금, 상속증여 등 은퇴 이후 금융상담 제공을 위해 KB국민은행의 KB골든라이프센터도 함께 운영된다.이와 함께 오는 2월에는 요양 상담과 연계한 돌봄 서비스와 시니어를 위한 최신 기술을 직접 체험할 수 있는 '에이지테크랩'도 오픈한다. 현장감 있는 체험 기반의 편의·안전·건강관리 솔루션을 통해 시니어 고객의 노후 생활에 대한 이해도를 높이고 합리적인 의사 결정을 돕는다.정문철 KB라이프 대표이사는 “시니어 고객의 삶은 요양과 금융으로 나뉘지 않는다. 돌봄·주거·건강·재무는 고객의 일상에서 하나의 여정으로 긴밀히 연결돼 있기 때문”이라며 “KB금융은 'KB라이프 역삼센터'를 중심으로 고객이 한 곳에서 노후 전반을 진단하고, 설계해 실질적인 준비로 이어갈 수 있는 새로운 경험을 제공할 것”이라고 말했다.</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>28</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DB손해보험</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>DB손해보험 'AI 에이전트' 서비스 출시, "보상서비스 품질 고도화" - 비즈니스포스트</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Thu, 19 Feb 2026 04:59:53 GMT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=430508</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>▲ DB손해보험이 '인공지능(AI) 에이전트' 서비스를 출시했다. &lt; DB손해보험 &gt;
+[비즈니스포스트] DB손해보험이 보험금 접수부터 지급까지 한 번에 처리해주는 인공지능(AI) 서비스를 내놨다.DB손해보험은 보험금 접수에 필요한 안내와 상황에 따른 맞춤형 응답을 제공하는 'AI 에이전트' 서비스를 출시했다고 19일 밝혔다.DB손해보험 AI 에이전트는 고객이 자동차 사고를 접수하면 30분 안에 초기 안내를 수행한다.이어 AI 에이전트가 취득한 정보를 바탕으로 보험금지급까지 원스톱 서비스를 제공한다.고객은 개인정보 활용에 동의하고 정비공장 정보, 치료 내용 및 병원 정보 등을 입력만 하면 된다.DB손해보험은 장기보상 청구 건에도 AI에이전트를 도입한다.AI 에이전트는 담보별 필요 서류가 미흡하면 관련 안내를 제공하고 비대면 서식 활용이 어려운 고객에게는 유선으로 개인정보 활용 동의를 받는다.DB손해보험 관계자는 “AI 기술은 단순한 보조수단이 아닌 고객 경험을 실질적으로 변화시키는 핵심 기술”이라며 “앞으로도 AI 기술로 보상서비스 품질을 고도화하고 금융소비자를 보호해 고객만족도를 높이겠다”고 말했다. 권영훈 기자</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/output/selected_news.xlsx
+++ b/output/selected_news.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,241 +468,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>보험사</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>우리은행</t>
+          <t>DB손해보험</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>우리은행, 생성형 AI 기반 '심층 리서치' 개발 - 초이스경제</t>
+          <t>DB손해보험, AI 도약 원년 선언…시스템 전반에 AI 적용 - 아주경제</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Wed, 25 Feb 2026 00:22:38 GMT</t>
+          <t>Wed, 18 Mar 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>http://www.choicenews.co.kr/news/articleView.html?idxno=161486</t>
+          <t>https://www.ajunews.com/view/20260318081724002</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>사진=우리은행
-[초이스경제 최유림 기자] 우리은행(은행장 정진완)은 "지난 23일 은행 내부 데이터를 활용해 보고서를 자동 생성하는 생성형 인공지능(AI) 기반 '심층 리서치(Deep Research)' 개발, AX 가속화에 나섰다"고 25일 밝혔다.
-우리은행에 따르면 이번에 도입한 '심층 리서치'는 직원의 산업·기업 분석 요청에 따라 내부 금융 데이터를 수집·연계·분석해 단시간 내 전문가 수준의 보고서 초안을 제시하는 지능형 보고서 작성 지원 시스템이다. 단순 정보 나열에 그치던 기존 AI와 달리 내부 핵심 데이터를 유기적으로 연결해 맥락을 이해하는 분석 결과를 도출하며, 자료 수집·정리 시간을 획기적으로 단축해 직원들이 보다 창의적이고 전략적인 의사결정에 집중할 수 있도록 지원하는 것이 특징이다.
-이와 함께, 우리은행은 글로벌 범용 AI인 MS 코파일럿과 자체 개발 '심층 리서치'를 전략적으로 결합해 AI 업무 환경을 한 단계 고도화했다. 코파일럿이 산업 동향·뉴스 등 외부 정보를 분석하는 데 강점이 있다면, '심층 리서치'는 은행 내부의 방대한 금융 데이터를 기반으로 최적화된 보고서를 생성한다. 이에 따라 외부 인사이트와 내부 데이터를 결합함으로써 분석의 정교함과 데이터 보안성을 동시에 확보했다.
-한편, 향후에는 '심층 리서치'를 고도화해 AI-Agent 기반 서비스로 확대 적용할 계획이다. △여신 심사 △자산관리 △내부통제 등 은행 핵심 업무 전반으로 AI 활용 범위를 넓혀 의사결정을 지원하는 '지능형 인공지능 비서' 체계로 발전시켜 나갈 방침이라고 우리은행은 덧붙였다.
-옥일진 우리은행 AX혁신그룹 부행장은 "이번 개발은 당행에 최적화된 독자적인 AI 역량을 확보했다는 데 의미가 있다"며 "앞으로도 직원들이 고부가가치 업무에 집중할 수 있도록 실무 밀착형 AI 서비스를 지속 확대해 나가겠다"고 말했다.</t>
+          <t>DB손해보험 사옥 [사진=DB손해보험]
+좋아요 0 나빠요 0
+DB손해보험이 올해를 인공지능(AI) 기반 도약을 위한 설계의 해로 운영한다는 방침이다.DB손보는 지난해 12월 1일부로 전략혁신본부 산하에 '데이터전략파트'를 'AI전략파트'로 명칭 변경하고 자문을 위한 'AI IMPACT 위원회'를 두고 있다. AI 전략 수립부터 실행까지 일원화된 체계를 만든다는 계획이다.DB손보는 그간 AI를 다양한 업무 영역에 적용해 실질적인 성과를 축적해 왔다. 고객센터 부문에서는 AI 기반 아웃바운드 콜 등 자동화 기술을 도입해 고객 응대 효율을 높였다. 업무 자동화 측면에서도 보험 심사와 보상, 내부 운영 프로세스 전반에 AI를 적용해 처리 시간을 단축하고 업무 품질을 개선하는 성과를 거두고 있다.지난 1월에는 금융산업 전반의 트렌드에 맞춘 고객 참여형 보상 시스템 'AI 에이전트(인공지능 로보텔러)' 시스템도 오픈했다. 삼성SDS와 협력해 개발한 'AI 에이전트'는 음성언어를 문자로 변환해주는 STT(Speech-To-Text), 문자를 음성언어로 변환해주는 TTS(Text-To- Speech) 기술을 기반으로 작동한다.DB손보 관계자는 "AI 기술은 단순한 보조수단이 아닌 고객 경험을 실질적으로 변화시키는 핵심 기술"이라며 "앞으로도 AI 기술을 기반으로 보상서비스 품질을 고도화하고 금융소비자 보호 및 고객만족도 향상을 위해 지속적으로 노력하겠다"고 말했다.
+©'5개국어 글로벌 경제신문' 아주경제. 무단전재·재배포 금지</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>은행</t>
+          <t>보험사</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>하나은행</t>
+          <t>KB손해보험</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>하나은행, AI 안부서비스 도입…"시니어의 건강한 일상 지원" - 파이낸셜신문</t>
+          <t>KB손해보험, 생성형 AI 전사 확산…디지털 혁신 가속 - 아주경제</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 23 Feb 2026 01:17:54 GMT</t>
+          <t>Wed, 18 Mar 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.efnews.co.kr/news/articleView.html?idxno=127687</t>
+          <t>https://www.ajunews.com/view/20260318082236011</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AI 목소리 든든이 통해 정기적으로 일상 안부 묻고 생활 정보도 제공
-하나은행이 시니어 고객의 건강한 일상을 지원하기 위해 인공지능(AI) 기반 맞춤형 전화 서비스인 'AI 안부서비스'를 도입하고 시범 운영에 나선다고 23일 밝혔다.
-AI 안부서비스는 AI 목소리 '든든이'가 고객이 정한 요일과 시간에 정기적으로 전화를 걸어 안부를 묻고 생활 정보를 제공하는 음성 통화 서비스다. 특히, 별도의 기기나 애플리케이션을 설치하지 않아도 돼 디지털 환경에 익숙하지 않은 시니어 고객도 편리하게 이용할 수 있다.
-(하나은행 제공)
-AI 목소리 든든이는 시니어들의 관심사와 생활 패턴을 반영해 맞춤형 대화 주제를 구성한다. 이를 통해 고객에게 간단한 건강 관리, 제철 음식, 문화·여가 등 일상에 도움이 되는 정보를 전달할 뿐만 아니라, 혼자 생활하거나 가족과 떨어져 지내는 고객에게 정서적 안정도 제공한다.
-서비스 신청 방법은 온·오프라인을 통해 하나더넥스트 상담을 받은 고객 중 선착순 300여 명에게 AI 안부서비스를 무료로 사용할 수 있는 쿠폰이 제공되고, 쿠폰에 안내된 웹 페이지를 통해 고객이 직접 서비스를 신청할 수 있다. 하나은행은 시범 운영 기간 중 고객 의견을 반영해 서비스 대상과 기능을 단계적으로 확대해 나갈 계획이다.
-이은정 하나은행 WM본부장은 "시니어 고객의 건강한 일상을 지원하고 디지털 포용성을 제고하기 위해 전화 기반의 AI 서비스를 새롭게 출시했다"며 "앞으로도 하나더넥스트를 중심으로 시니어 고객의 금융은 물론 일상까지 함께 지원하는 다양한 서비스를 지속적으로 선보이겠다"고 말했다.
-한편, 하나금융그룹의 시니어 특화 브랜드인 하나더넥스트는 은퇴 설계, 자산관리, 상속·증여 등 생애 전반에 걸친 금융 솔루션과 라이프케어 서비스를 제공하고 있다. 상담을 원하는 고객은 ARS, 하나더넥스트 공식 홈페이지, 하나원큐 앱 등을 통해 신청할 수 있다. [파이낸셜신문=임영빈 기자]
-저작권자 © 파이낸셜신문 무단전재 및 재배포 금지</t>
+          <t>서울 강남구 KB손해보험 본사 [사진=KB손해보험]
+좋아요 0 나빠요 0
+KB손해보험이 생성형 인공지능(AI)을 활용한 디지털 전환을 넘어 전사 차원의 'AI 내재화'에 속도를 내고 있다.KB손보는 KB금융그룹이 구축한 'KB GenAI 포털'을 기반으로 임직원의 업무 생산성을 높일 수 있는 다양한 과제를 발굴해왔다고 밝혔다.KB손보는 머신러닝 기반의 예측 모델을 활용해 고객이탈 위험, 계약갱신 가능성, 우·불량 고객분류 등의 업무를 수행하고 있다.KB손보는 AI 기술이 보험 업무 전반에 자연스럽게 스며들 수 있도록 단계적이고 체계적인 전략을 마련하고 있다. 업무 효율성 제고는 물론 고객경험까지 혁신하는 KB손보만의 디지털 전환을 지속 추진해 나갈 계획이다.지난해 초 조직개편에서 'AI데이터분석 파트'를 신설해 보험 서비스 전반의 디지털 전환을 체계적으로 추진할 수 있는 기반을 마련하기도 했다.AI 화법 코칭 솔루션인 크디랩의 '쏘카인드(Sokind)'도 영업 교육 현장에 도입했다. 이 프로그램은 고객 응대 과정에서 나타나는 설계사의 언어, 음성, 표정, 시선, 습관어 등 다양한 대화 요소를 AI가 실시간으로 분석하고, 이에 대한 맞춤형 피드백을 제공한다.KB손보 관계자는 "생성형 AI를 통한 업무 혁신은 단순히 업무 효율성 향상에 그치는 것이 아니라 정확하고 일관된 서비스 제공으로 고객 만족도를 높이는 데 있다"며 "앞으로도 보험 비즈니스의 전 영역에서 AI 기반 디지털 혁신을 지속 추진하겠다"고 말했다.
+©'5개국어 글로벌 경제신문' 아주경제. 무단전재·재배포 금지</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>카드사</t>
+          <t>보험사</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NH농협카드</t>
+          <t>메리츠화재</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>농협은행, 'AI, 금융 일상에' 전면 전략 전환... 에이전틱 AI 뱅크 선언 - 프레스맨</t>
+          <t>인스웨이브, 한·미 특허 연이어 획득…"AI·UI 기술로 글로벌 시장 정조준" - 지디넷코리아</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Fri, 13 Feb 2026 12:59:51 GMT</t>
+          <t>Wed, 18 Mar 2026 08:15:19 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.pressman.kr/news/articleView.html?idxno=99995</t>
+          <t>https://zdnet.co.kr/view/?no=20260318171519</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>디자인=김승종기자/이미지=농협은행, 게티이미지뱅크
-NH농협은행이 AI를 은행 운영의 핵심 축으로 삼는 'Agentic AI Bank(에이전틱 AI 뱅크)' 전환을 전면 선언했다. 6,200억원 규모의 코어뱅킹 재구축 프로젝트와 AI 무인점포, 원화 스테이블코인 생태계 구축까지 올해 들어 AI 중심의 디지털 혁신을 동시다발적으로 추진하고 있다. '2026년은 AI 에이전트의 해'라는 글로벌 금융권 트렌드를 국내 시중은행 중 가장 적극적으로 선점하겠다는 포석이다.
-'AI Agent First'... 글로벌 트렌드 선점
-NH농협은행 AI데이터부문은 지난달 서울 본사에서 '사업추진 결의대회'를 열고 'Agentic AI Bank'로의 본격 도약을 선언했다. 'AI가 고객들의 금융 일상에 자연스레 스며드는 은행'을 만들겠다는 비전이다.
-이날 결의대회에서는 'AI Agent First' 전략을 중심으로 금융서비스 혁신 방향을 논의했다. AI기본법, STO(토큰증권) 법제화 등 규제 동향과 AI 트렌드 강연도 진행해 임직원들의 사업 추진 역량을 강화했다.
-'에이전틱 AI(Agentic AI)'는 사람의 지시 없이도 스스로 판단하고 업무를 수행하는 자율형 AI를 의미한다.
-액센추어의 '2026 은행업 트렌드' 보고서에 따르면, 향후 3년 내 57%의 은행 임원이 AI 에이전트가 리스크·컴플라이언스·감사, 사기 탐지, 거래 모니터링 기능에 완전히 내재화될 것으로 전망했다. 56%는 신용평가·대출 심사, 고객확인(KYC) 영역까지 AI 에이전트가 광범위하게 도입될 것으로 예상했다.
-김주식 농협은행 AI데이터부문 부행장은 "고객을 미소짓게 하고 고객과의 동반성장을 실현하는 농협은행을 만들기 위해 전사적 AX(AI 전환)를 지속적으로 추진하겠다"고 밝혔다.
-6,200억 투입 '프로젝트 NEO'... 코어뱅킹 전면 재구축
-농협은행의 AI 전환 전략의 근간은 코어뱅킹 시스템 전면 개편이다. 농협은행은 지난달 경기도 의왕 NH통합IT센터에서 '프로젝트 NEO' 본사업에 착수한다고 밝혔다.
-프로젝트 NEO는 'Next, Evolutionary, Omni-Banking'의 약자로, 총 6,200억원을 투자해 2028년 1월까지 계정계 시스템을 전면 재구축하는 사업이다. 2024년부터 추진해온 차세대 프로젝트의 최종 단계로, 금융권 차세대 사업 중 단일 계약 규모로는 최대 수준이다. LG CNS가 사업을 맡아 27개월간 진행한다.
-주요 개선 사항은 ▲IT 기술 구조 전면 개편 ▲비대면·대면 통합 프로세스 구현 ▲금융상품 관리시스템 개선 ▲사용자 중심 엔드 투 엔드(End to End) 프로세스 자동화 ▲고객 서식·서류의 디지털 관리체계 구축 등이다.
-LG CNS는 금융거래 시스템을 업무 단위별로 분리해 독립 운영이 가능한 구조로 전환하고 비대면 전용 코어뱅킹 시스템을 별도 구축한다. AI 보안 솔루션 '시큐엑스퍼(SecuXper) AI'와 시스템 검증 솔루션 '퍼펙트윈(PerfecTwin)' 등 자체 기술도 적용된다.
-정동훤 농협은행 테크솔루션부문 부행장은 "이번 사업은 농협은행 계정계 혁신의 중심점이 될 것"이라며 "성공적인 사업 완수를 통해 초개인화 금융으로 고객을 미소짓게 하겠다"고 밝혔다.
-AI가 먼저 인사하는 은행... 'NH디지털스테이션' 개점
-코어뱅킹 개편과 함께 고객 접점에서의 AI 혁신도 본격화됐다. 농협은행은 지난달 말 AI 기술을 접목한 미래형 무인점포 'NH디지털스테이션' 위례점을 개점했다.
-NH디지털스테이션은 AI 기반 차세대 금융기기 'NH AI STM(Smart Teller Machine)'을 중심으로 화상상담 디지털데스크와 ATM을 갖춘 무인점포다.
-가장 눈에 띄는 점은 쌍방향 금융 서비스 구현이다. 고객이 기기 앞에 서면 AI가 얼굴을 인식해 먼저 인사와 안내를 시작한다. 단순히 화면을 보고 조작하던 기존 방식을 넘어, LLM(대규모언어모델) 기반으로 고객과 기기가 실시간 대화하며 금융 거래를 지시하거나 궁금한 점에 대한 답을 얻을 수 있다.
-NH AI STM은 입출금, 이체, 체크카드 발급 등 총 17종의 업무를 지원한다. 얼굴과 장정맥을 활용한 다중 생체인증을 적용해 카드나 통장 없이도 안전한 거래가 가능하다. 전산 조작에 익숙하지 않은 고령층과 장애인 등 금융취약계층의 이용 문턱을 낮추는 데도 기여할 전망이다.
-농협은행은 위례점을 시작으로 주요 거점에 디지털 무인점포와 NH AI STM 서비스를 순차적으로 확대해 나갈 계획이다.
-원화 스테이블코인 생태계 구축... 글로벌 블록체인과 연결
-농협은행의 AI 전환 전략은 디지털자산 영역까지 확장되고 있다. 농협은행은 지난 2일 글로벌 디지털자산 인프라 기업 파이어블록스(Fireblocks)와 '택스리펀드 디지털화 PoC와 원화 스테이블코인 생태계 구성방안'을 주제로 전략 미팅을 진행했다.
-이번 미팅에는 농협은행 AI데이터부문 임원과 파이어블록스 본사 스테픈 리차드슨(Stephen Richardson) 전략담당임원(CSO)을 비롯한 글로벌·아시아 세일즈 책임자들이 참석했다.
-양사가 진행 중인 '택스리펀드 디지털화 PoC'는 지난해 11월 착수해 올해 1월 설계를 마무리했으며, 4월까지 개발과 테스트를 완료할 예정이다.
-해외 관광객이 종이 서류로 부가세를 환급받던 절차를 블록체인 기반으로 디지털화하는 프로젝트다. 파이어블록스, 아발란체(Avalanche), 마스터카드, 월드페이 등 글로벌 기술·결제 기업과 공동으로 추진하고 있다.
-양사는 원화 스테이블코인이 금융 인프라와 디지털자산 서비스 전반을 연결하는 핵심 결제레일(Payment Rail)로 발전할 수 있다는 점에 공감했다. 은행 중심의 신뢰 기반 구조를 글로벌 블록체인 네트워크와 결합하는 협력 모델을 구체화하고 있다.
-이와 별도로 농협은행은 자체 EVM(이더리움 가상머신) 기반 블록체인 메인넷을 활용해 스테이블코인과 STO에 토큰 프로토콜을 적용하는 PoC도 추진 중이다. K팝 저작권 등을 기초자산으로 한 토큰증권 청약·배정·청산 전 과정을 설계·테스트하고 있다.
-농협은행 관계자는 "원화 스테이블코인을 중심으로 한 디지털자산 생태계 구축을 통해 제도화 방향성에 맞춰 글로벌 금융 인프라와의 연결과 국내 금융 혁신을 동시에 추진하겠다"고 밝혔다.
-농협은행의 이 같은 행보는 글로벌 금융권의 흐름과 맞닿아 있다. 2026년은 AI 에이전트가 파일럿 단계를 넘어 본격적인 프로덕션 스케일로 확대되는 해가 될 것으로 전망된다.
-농협은행은 코어뱅킹 재구축(프로젝트 NEO), AI 무인점포(NH디지털스테이션), 디지털자산 생태계(원화 스테이블코인)라는 세 축을 중심으로 'Agentic AI Bank' 전환을 가속화할 계획이다. AI가 단순 보조 도구가 아니라 금융 서비스의 핵심 운영 체계로 자리잡는 '초연결 디지털 네이티브 뱅크'를 목표로 하고 있다. [프레스맨]
-저작권자 © 프레스맨 무단전재 및 재배포 금지</t>
+          <t>인스웨이브가 국내와 미국 특허를 확보하며 금융 인공지능(AI)와 사용자 인터페이스(UI) 개발 글로벌 경쟁력을 강화했다.
+인스웨이브는 AI 기반 금융 단말 시스템과 UI 플랫폼 개발 기술에 대한 국내외 특허를 확보하며 기술 경쟁력을 한층 끌어올렸다고 17일 밝혔다.
+이번 성과는 금융 업무 자동화와 UI 개발 효율화를 동시에 겨냥한 것으로, 글로벌 시장 진출 기반을 강화했다는 평가다.
+인스웨이브, 한·미 특허 연이어 획득(이미지=인스웨이브)
+이번에 등록된 국내 특허는 AI가 금융기관의 복잡한 업무를 분석하고 최적의 처리 절차를 구성하는 기술이다. 대출 등 주요 업무에서 반복되던 수작업을 줄이고 OCR과 공공 API를 연계해 업무 흐름을 자동화한 점이 핵심이다. 해당 기술은 인스웨이브의 금융 단말 플랫폼 '웹탑'에 적용돼 금융권의 AI 도입을 실질적으로 지원하는 기반으로 활용되고 있다.
+미국 특허는 UI 플랫폼 '웹스퀘어 AI' 통합 개발 기술이다. 화면 설계 결과를 자동으로 경량 웹 코드로 변환하고 최적화해, 하나의 소스로 다양한 기기와 브라우저를 지원할 수 있도록 했다. 이른바 OSMU 구조를 구현한 것으로, 복잡한 UI 개발 과정을 단순화하고 운영 효율을 높이는 데 초점을 맞췄다.
+이번 특허 확보로 인스웨이브는 금융 단말과 UI 플랫폼 양측 핵심 제품에 대한 기술 보호 체계를 구축했다. NH농협은행, 하나은행, 메리츠화재 등 주요 고객사에 공급 중인 솔루션에도 해당 기술이 적용되면서, 국내 시장 경쟁력 유지와 함께 해외 진출 시 기술 장벽 확보 효과도 기대된다.
+관련기사
+인스웨이브는 대화형 서비스, 앱 개발 자동화, 재사용 UI 기술 등 다양한 특허를 기반으로 AX 기업으로의 전환을 추진하고 있다. 이번 특허 추가로 지식재산권 경쟁력을 더욱 강화할 전망이다.
+어세룡 대표는 "국내 AI 기술과 미국 UI 플랫폼 특허를 동시에 확보하며 기술력을 글로벌 수준에서 인정받았다"며 "핵심 기술을 기반으로 금융 현장의 AI 전환을 가속하고 해외 시장 확대에도 속도를 낼 것"이라고 밝혔다.</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>[금융 AI 대전환②] 신한, 1부서 1에이전트로 AX 전면화…거버넌스도 정비 - v.daum.net</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Sat, 14 Feb 2026 15:02:20 GMT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://v.daum.net/v/20260215000220771?f=p</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>조직 학습 구조 전환 시동…현업이 직접 설계·적용
-신한금융그룹이 '1부서 1에이전트' 전략을 통해 현업 주도형 인공지능 전환(AX) 전략을 본격화하고 있다. /신한금융그룹
-금융산업은 데이터와 리스크를 축으로 움직이는 대표적 데이터 산업이다. 고금리·저성장 기조가 구조화되면서 금융회사들은 비용 효율화, 정교한 리스크 관리, 초개인화된 고객 서비스라는 복합 과제를 동시에 떠안고 있다. 인공지능(AI)은 이 난제를 풀 핵심 수단으로 부상했다. 금융당국이 생성형 AI와 클라우드, 업무 자동화 기술의 활용 범위를 단계적으로 넓히면서 금융권의 AI 전환은 파일럿을 넘어 현업 전반으로 확산되는 국면이다. &lt;더팩트&gt;는 5대 금융지주의 AI 전략과 투자 방향을 비교·분석하고 금융 AI 전환이 실질적인 경쟁력 강화로 이어지고 있는지를 들여다본다. 아울러 내부통제와 인력 재배치 등 구조적 과제가 무엇인지도 함께 짚어본다. &lt;편집자주&gt;
-[더팩트 | 김태환 기자] 신한금융그룹이 인공지능(AI)을 일부 부서의 실험 단계에서 전사 업무 체계로 확산하는 '현업 주도형 AX(인공지능 전환)' 전략을 본격화하고 있다. 그룹 차원의 AI 윤리 원칙과 위험관리 체계를 정비하는 동시에, 모든 부서가 AI를 직접 업무에 접목하도록 유도하는 '1부서 1 에이전트(Agent)' 캠페인을 추진하며 실행력 강화에 나선 모습이다.
-신한금융은 인공지능 전환(AX)과 디지털 전환(DX)을 선택적 혁신 과제가 아닌 그룹 경쟁력과 직결된 전략 과제로 인식하고 있다. 고금리·저성장 환경에서 비용 효율화와 리스크 관리, 고객 맞춤형 서비스 고도화라는 복합 과제를 동시에 풀어야 하는 상황에서 AI를 핵심 실행 수단으로 삼겠다는 구상이다. 단순 기술 도입이 아니라 '일하는 방식'과 '사업 방식'의 전환을 촉발하는 변수로 규정했다는 점이 특징이다.
-AX 가속화와 함께 신한금융은 그룹 차원의 AI 거버넌스를 구축했다. AI 윤리 원칙을 제정하고, 각 계열사 업무 특성에 맞는 위험관리 체계를 구체화했다.
-특히 준법·정보보호·소비자보호·리스크 담당 임원이 참여하는 그룹 협의체를 구성해 AI 활용 전반에 대한 정책을 공유·조율하고 있다. AI 모델 도입과 서비스 확산이 내부통제 체계 밖으로 벗어나지 않도록 사전 점검과 승인·모니터링 절차를 병행한다는 설명이다.
-AI 활용 측면에서는 외부 상용 모델과 내부 자체 모델을 병행하는 하이브리드 방식을 택했다. 서비스 특성과 민감도에 따라 모델을 선택적으로 적용해 효율성과 보안을 동시에 확보하겠다는 구상이다.
-동시에 전 직원이 활용 가능한 AI 기반 인프라를 구축해 현업 접근성을 높이고 있다. 특정 부서나 디지털 조직에 국한된 프로젝트가 아니라, 전사적 업무 도구로 정착시키겠다는 방향성이다.
-신한금융은 SaaS 망분리 규제 완화, 금융권 AI 위험관리 프레임워크 등 제도 환경 변화를 지속 모니터링하고 있다. /신한금융그룹
-올해 신한금융은 전 그룹사를 대상으로 '1부서 1 에이전트(Agent)' 캠페인을 추진한다. AI 에이전트는 반복 업무나 문서 작성 등에만 자동화가 이루어진 것이 아니라 업무 프로세스 전 과정을 스스로 판단하고 분석하는 자동화 단계의 AI를 의미한다.
-예를 들어, 생성형 AI의 경우 "연체율 추이를 알려줘"라고 지시하면, 관련 보고서를 요약하는 수준에 그친다. AI 에이전트는 같은 질문에 대해 데이터 조회, 분석, 보고서 작성, 메일 발송, 업무 내용 저장 등 더욱 능동적으로 업무를 보조하게 된다.
-이러한 AI에이전트를 1부서별 1개씩 배치한다면 모든 부서가 본인 업무에 AI를 접목하고, 각 조직 특성에 맞는 AI 활용 사례를 발굴·적용하도록 유도할 수 있다는 설명이다.
-더 나아가 본격적으로 다가올 AI 에이전트 시대에 대비해 현업이 직접 문제를 정의하고 솔루션을 설계하는 구조를 만들어갈 수 있다고 신한금융은 설명한다. 중앙 조직이 일괄 개발해 배포하는 방식이 아니라, 현업 주도 실행 모델을 통해 조직 학습 효과를 축적하겠다는 전략으로 풀이된다.
-아울러 신한금융은 SaaS 망분리 규제 완화, 금융권 AI 위험관리 프레임워크 등 제도 환경 변화를 지속 모니터링하고 있다. AI 활용이 확대될수록 규제·승인 절차의 민첩성 역시 중요해질 수밖에 없다는 판단이다.
-신한금융 관계자는 "금융회사의 책임성 확보를 전제로 정책적 지원이 병행될 경우, AI 도입 속도와 서비스 혁신 범위가 한층 확대될 수 있다"고 설명했다.
-금융업계 관계자는 "신한금융의 전사적 AX 전략이 실제 성과로 이어지기 위해서는 데이터 품질 고도화, 현업 역량 축적, 위험관리 정교화가 병행돼야 한다는 과제도 남는다"면서 "확산의 속도와 통제의 균형을 어떻게 맞추느냐가 신한 AX 전략의 성패를 가를 변수로 떠오르고 있다"고 말했다.
-kimthin@tf.co.kr
-발로 뛰는 더팩트는 24시간 여러분의 제보를 기다립니다.
-▶카카오톡: '더팩트제보' 검색
-▶이메일: jebo@tf.co.kr
-▶뉴스 홈페이지: http://talk.tf.co.kr/bbs/report/write</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>보험사</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DB손해보험</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DB손해보험 'AI 에이전트' 서비스 출시, "보상서비스 품질 고도화" - 비즈니스포스트</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Thu, 19 Feb 2026 04:59:53 GMT</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://www.businesspost.co.kr/BP?command=article_view&amp;num=430508</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>▲ DB손해보험이 '인공지능(AI) 에이전트' 서비스를 출시했다. &lt; DB손해보험 &gt;
-[비즈니스포스트] DB손해보험이 보험금 접수부터 지급까지 한 번에 처리해주는 인공지능(AI) 서비스를 내놨다.DB손해보험은 보험금 접수에 필요한 안내와 상황에 따른 맞춤형 응답을 제공하는 'AI 에이전트' 서비스를 출시했다고 19일 밝혔다.DB손해보험 AI 에이전트는 고객이 자동차 사고를 접수하면 30분 안에 초기 안내를 수행한다.이어 AI 에이전트가 취득한 정보를 바탕으로 보험금지급까지 원스톱 서비스를 제공한다.고객은 개인정보 활용에 동의하고 정비공장 정보, 치료 내용 및 병원 정보 등을 입력만 하면 된다.DB손해보험은 장기보상 청구 건에도 AI에이전트를 도입한다.AI 에이전트는 담보별 필요 서류가 미흡하면 관련 안내를 제공하고 비대면 서식 활용이 어려운 고객에게는 유선으로 개인정보 활용 동의를 받는다.DB손해보험 관계자는 “AI 기술은 단순한 보조수단이 아닌 고객 경험을 실질적으로 변화시키는 핵심 기술”이라며 “앞으로도 AI 기술로 보상서비스 품질을 고도화하고 금융소비자를 보호해 고객만족도를 높이겠다”고 말했다. 권영훈 기자</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
